--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N62_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N62_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>50.40299458453727</v>
+        <v>8.190486619987306</v>
       </c>
       <c r="D2" t="n">
-        <v>50.22555167869364</v>
+        <v>8.161652147787716</v>
       </c>
       <c r="E2" t="n">
-        <v>7.74902246492252</v>
+        <v>1.25921615054991</v>
       </c>
       <c r="F2" t="n">
-        <v>7.734669950061376</v>
+        <v>1.256883866884974</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.33133071338644</v>
+        <v>6.553841240925297</v>
       </c>
       <c r="D3" t="n">
-        <v>40.11754342737585</v>
+        <v>6.519100806948575</v>
       </c>
       <c r="E3" t="n">
-        <v>7.74902246492252</v>
+        <v>1.25921615054991</v>
       </c>
       <c r="F3" t="n">
-        <v>7.734669950061376</v>
+        <v>1.256883866884974</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.953363280489</v>
+        <v>6.817421533079463</v>
       </c>
       <c r="D4" t="n">
-        <v>41.88464628121406</v>
+        <v>6.806255020697285</v>
       </c>
       <c r="E4" t="n">
-        <v>7.74902246492252</v>
+        <v>1.25921615054991</v>
       </c>
       <c r="F4" t="n">
-        <v>7.734669950061376</v>
+        <v>1.256883866884974</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.30004286576134</v>
+        <v>3.948756965686218</v>
       </c>
       <c r="D5" t="n">
-        <v>24.1560569246012</v>
+        <v>3.925359250247694</v>
       </c>
       <c r="E5" t="n">
-        <v>7.74902246492252</v>
+        <v>1.25921615054991</v>
       </c>
       <c r="F5" t="n">
-        <v>7.734669950061376</v>
+        <v>1.256883866884974</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.65328120318518</v>
+        <v>5.143658195517592</v>
       </c>
       <c r="D6" t="n">
-        <v>31.51661126524012</v>
+        <v>5.121449330601519</v>
       </c>
       <c r="E6" t="n">
-        <v>7.74902246492252</v>
+        <v>1.25921615054991</v>
       </c>
       <c r="F6" t="n">
-        <v>7.734669950061376</v>
+        <v>1.256883866884974</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>40.97533002395882</v>
+        <v>6.658491128893308</v>
       </c>
       <c r="D7" t="n">
-        <v>40.82769738960388</v>
+        <v>6.634500825810631</v>
       </c>
       <c r="E7" t="n">
-        <v>7.74902246492252</v>
+        <v>1.25921615054991</v>
       </c>
       <c r="F7" t="n">
-        <v>7.734669950061376</v>
+        <v>1.256883866884974</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>29.48536122353735</v>
+        <v>4.791371198824819</v>
       </c>
       <c r="D8" t="n">
-        <v>29.46592564428495</v>
+        <v>4.788212917196304</v>
       </c>
       <c r="E8" t="n">
-        <v>7.74902246492252</v>
+        <v>1.25921615054991</v>
       </c>
       <c r="F8" t="n">
-        <v>7.734669950061376</v>
+        <v>1.256883866884974</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>38.85287533383803</v>
+        <v>6.31359224174868</v>
       </c>
       <c r="D9" t="n">
-        <v>38.95553279285521</v>
+        <v>6.330274078838972</v>
       </c>
       <c r="E9" t="n">
-        <v>7.74902246492252</v>
+        <v>1.25921615054991</v>
       </c>
       <c r="F9" t="n">
-        <v>7.734669950061376</v>
+        <v>1.256883866884974</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
